--- a/outputs/evaluation/decision/v1/CF_M01/CF_M01_decision_eval_avg.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/CF_M01_decision_eval_avg.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3778</v>
+        <v>0.7083</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5</v>
+        <v>0.8095</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8733</v>
+        <v>0.9223</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1667</v>
+        <v>0.5778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9167</v>
+        <v>0.6222</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9302</v>
+        <v>0.9651</v>
       </c>
     </row>
     <row r="8">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3333</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5.6667</v>
       </c>
     </row>
     <row r="5">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3333</v>
+        <v>2.3333</v>
       </c>
     </row>
     <row r="6">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1.3333</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3778</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>0.8095</v>
       </c>
     </row>
     <row r="9">

--- a/outputs/evaluation/decision/v1/CF_M01/CF_M01_decision_eval_avg.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/CF_M01_decision_eval_avg.xlsx
@@ -446,13 +446,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7083</v>
+        <v>0.3074</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8095</v>
+        <v>0.3333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9223</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="5">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.5778</v>
+        <v>0.2222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6222</v>
+        <v>0.6389</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9651</v>
+        <v>0.9302</v>
       </c>
     </row>
     <row r="8">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6667</v>
+        <v>2.3333</v>
       </c>
     </row>
     <row r="5">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.3333</v>
+        <v>5.6667</v>
       </c>
     </row>
     <row r="6">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.3333</v>
+        <v>4.6667</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7083</v>
+        <v>0.3074</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8095</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="9">
